--- a/koboforms/actiondesign.xlsx
+++ b/koboforms/actiondesign.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/deo/anticipatoryactiondecisions/koboforms/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/deo/aadecisionoverview/koboforms/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66B3B43B-B0CD-F948-A479-4F0B317D473F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A410D91D-2944-1B4A-8383-9A536DCFFE5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2760" yWindow="-18260" windowWidth="28040" windowHeight="17440" xr2:uid="{05574417-E28B-7A44-8D51-6FA488FA6DA5}"/>
+    <workbookView xWindow="5000" yWindow="-17940" windowWidth="28040" windowHeight="17440" xr2:uid="{05574417-E28B-7A44-8D51-6FA488FA6DA5}"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="36">
   <si>
     <t>type</t>
   </si>
@@ -114,9 +114,6 @@
     <t>q6</t>
   </si>
   <si>
-    <t>q7</t>
-  </si>
-  <si>
     <t>q8</t>
   </si>
   <si>
@@ -126,14 +123,6 @@
     <t>multiline</t>
   </si>
   <si>
-    <t>Do you choose to make an action trigger based on the 40% trigger as is, for proc
-uring and distributing seeds?</t>
-  </si>
-  <si>
-    <t>Do you choose to make an action trigger that triggers less often, only in the st
-rongest forecast to reduce false alarms?</t>
-  </si>
-  <si>
     <t>Would you want to make an expensive acton trigger that occurs 60% of the time, including the new action year of 2015?</t>
   </si>
   <si>
@@ -150,6 +139,12 @@
   </si>
   <si>
     <t>ActionDesign</t>
+  </si>
+  <si>
+    <t>Do you choose to make an action trigger based on the 40% trigger as is, for procuring and distributing seeds?</t>
+  </si>
+  <si>
+    <t>Do you choose to make an action trigger that triggers less often, only in the strongest forecast to reduce false alarms?</t>
   </si>
 </sst>
 </file>
@@ -534,7 +529,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{994C7F9E-9867-6243-AAB9-77628DC2993D}">
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="49.1640625" style="6" customWidth="1"/>
@@ -579,16 +574,16 @@
         <v>11</v>
       </c>
       <c r="C3" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" t="s">
         <v>27</v>
       </c>
-      <c r="D3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="51" x14ac:dyDescent="0.2">
+    </row>
+    <row r="4" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>23</v>
       </c>
@@ -596,7 +591,7 @@
         <v>12</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D4" t="s">
         <v>4</v>
@@ -610,7 +605,7 @@
         <v>19</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D5" t="s">
         <v>4</v>
@@ -624,7 +619,7 @@
         <v>20</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D6" t="s">
         <v>4</v>
@@ -638,7 +633,7 @@
         <v>21</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D7" t="s">
         <v>4</v>
@@ -646,19 +641,19 @@
     </row>
     <row r="8" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="B8" t="s">
         <v>24</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D8" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="68" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -666,24 +661,13 @@
         <v>25</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D9" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" ht="34" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" t="s">
-        <v>26</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="D10" t="s">
-        <v>4</v>
+      <c r="E9" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -752,10 +736,10 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C2" t="s">
         <v>8</v>

--- a/koboforms/actiondesign.xlsx
+++ b/koboforms/actiondesign.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/deo/aadecisionoverview/koboforms/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A410D91D-2944-1B4A-8383-9A536DCFFE5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EB39453-443D-DF43-B9ED-A1C388E5D21E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5000" yWindow="-17940" windowWidth="28040" windowHeight="17440" xr2:uid="{05574417-E28B-7A44-8D51-6FA488FA6DA5}"/>
   </bookViews>
